--- a/artfynd/A 65389-2021 artfynd.xlsx
+++ b/artfynd/A 65389-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 65389-2021 artfynd.xlsx
+++ b/artfynd/A 65389-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY76"/>
+  <dimension ref="A1:AY49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5228,10 +5228,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>112605504</v>
+        <v>112610152</v>
       </c>
       <c r="B41" t="n">
-        <v>5473</v>
+        <v>91032</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5240,38 +5240,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>101410</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Åmsele, Vb</t>
+          <t>Holmträsk, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>713143</v>
+        <v>713174</v>
       </c>
       <c r="R41" t="n">
-        <v>7163543</v>
+        <v>7163501</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5335,7 +5335,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>112605508</v>
+        <v>112610155</v>
       </c>
       <c r="B42" t="n">
         <v>78448</v>
@@ -5371,14 +5371,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Åmsele, Vb</t>
+          <t>Holmträsk, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>713204</v>
+        <v>713142</v>
       </c>
       <c r="R42" t="n">
-        <v>7163427</v>
+        <v>7163574</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5442,7 +5442,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>112605485</v>
+        <v>112610145</v>
       </c>
       <c r="B43" t="n">
         <v>91032</v>
@@ -5478,14 +5478,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Åmsele, Vb</t>
+          <t>Holmträsk, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>713274</v>
+        <v>713230</v>
       </c>
       <c r="R43" t="n">
-        <v>7163512</v>
+        <v>7163429</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5549,10 +5549,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>112605494</v>
+        <v>112610147</v>
       </c>
       <c r="B44" t="n">
-        <v>77527</v>
+        <v>91055</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5565,34 +5565,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>5966</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Åmsele, Vb</t>
+          <t>Holmträsk, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>713426</v>
+        <v>713310</v>
       </c>
       <c r="R44" t="n">
-        <v>7163462</v>
+        <v>7163504</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5656,10 +5656,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>112605503</v>
+        <v>112610151</v>
       </c>
       <c r="B45" t="n">
-        <v>91032</v>
+        <v>78448</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5668,38 +5668,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Åmsele, Vb</t>
+          <t>Holmträsk, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>713155</v>
+        <v>713221</v>
       </c>
       <c r="R45" t="n">
-        <v>7163539</v>
+        <v>7163494</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5763,10 +5763,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>112605488</v>
+        <v>112610146</v>
       </c>
       <c r="B46" t="n">
-        <v>91032</v>
+        <v>77608</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5775,38 +5775,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Åmsele, Vb</t>
+          <t>Holmträsk, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>713228</v>
+        <v>713272</v>
       </c>
       <c r="R46" t="n">
-        <v>7163431</v>
+        <v>7163536</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5870,10 +5870,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>112605487</v>
+        <v>112610156</v>
       </c>
       <c r="B47" t="n">
-        <v>91032</v>
+        <v>77609</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5882,38 +5882,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Åmsele, Vb</t>
+          <t>Holmträsk, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>713209</v>
+        <v>713141</v>
       </c>
       <c r="R47" t="n">
-        <v>7163472</v>
+        <v>7163575</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5977,10 +5977,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>112610152</v>
+        <v>112610153</v>
       </c>
       <c r="B48" t="n">
-        <v>91032</v>
+        <v>77527</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5989,25 +5989,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6017,10 +6017,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>713174</v>
+        <v>713202</v>
       </c>
       <c r="R48" t="n">
-        <v>7163501</v>
+        <v>7163525</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6084,10 +6084,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>112605501</v>
+        <v>112610150</v>
       </c>
       <c r="B49" t="n">
-        <v>77609</v>
+        <v>88855</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6100,34 +6100,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>1962</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Åmsele, Vb</t>
+          <t>Holmträsk, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>713139</v>
+        <v>713222</v>
       </c>
       <c r="R49" t="n">
-        <v>7163574</v>
+        <v>7163450</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6188,2895 +6188,6 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>112605410</v>
-      </c>
-      <c r="B50" t="n">
-        <v>91018</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>3100</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Talltaggsvamp</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Bankera fuligineoalba</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>Åmsele, Vb</t>
-        </is>
-      </c>
-      <c r="Q50" t="n">
-        <v>713334</v>
-      </c>
-      <c r="R50" t="n">
-        <v>7163482</v>
-      </c>
-      <c r="S50" t="n">
-        <v>10</v>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>2022-11-03</t>
-        </is>
-      </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>2022-11-03</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT50" t="inlineStr"/>
-      <c r="AW50" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>112605505</v>
-      </c>
-      <c r="B51" t="n">
-        <v>77608</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>6446</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Carbonicola anthracophila</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>Åmsele, Vb</t>
-        </is>
-      </c>
-      <c r="Q51" t="n">
-        <v>713192</v>
-      </c>
-      <c r="R51" t="n">
-        <v>7163462</v>
-      </c>
-      <c r="S51" t="n">
-        <v>10</v>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT51" t="inlineStr"/>
-      <c r="AW51" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>112610155</v>
-      </c>
-      <c r="B52" t="n">
-        <v>78448</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>Holmträsk, Vb</t>
-        </is>
-      </c>
-      <c r="Q52" t="n">
-        <v>713142</v>
-      </c>
-      <c r="R52" t="n">
-        <v>7163574</v>
-      </c>
-      <c r="S52" t="n">
-        <v>10</v>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W52" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT52" t="inlineStr"/>
-      <c r="AW52" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>112605506</v>
-      </c>
-      <c r="B53" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>Åmsele, Vb</t>
-        </is>
-      </c>
-      <c r="Q53" t="n">
-        <v>713190</v>
-      </c>
-      <c r="R53" t="n">
-        <v>7163460</v>
-      </c>
-      <c r="S53" t="n">
-        <v>10</v>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W53" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT53" t="inlineStr"/>
-      <c r="AW53" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>112610145</v>
-      </c>
-      <c r="B54" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>Holmträsk, Vb</t>
-        </is>
-      </c>
-      <c r="Q54" t="n">
-        <v>713230</v>
-      </c>
-      <c r="R54" t="n">
-        <v>7163429</v>
-      </c>
-      <c r="S54" t="n">
-        <v>10</v>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT54" t="inlineStr"/>
-      <c r="AW54" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>112605493</v>
-      </c>
-      <c r="B55" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>Åmsele, Vb</t>
-        </is>
-      </c>
-      <c r="Q55" t="n">
-        <v>713448</v>
-      </c>
-      <c r="R55" t="n">
-        <v>7163469</v>
-      </c>
-      <c r="S55" t="n">
-        <v>10</v>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AA55" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT55" t="inlineStr"/>
-      <c r="AW55" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>112605498</v>
-      </c>
-      <c r="B56" t="n">
-        <v>78448</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>Åmsele, Vb</t>
-        </is>
-      </c>
-      <c r="Q56" t="n">
-        <v>713209</v>
-      </c>
-      <c r="R56" t="n">
-        <v>7163486</v>
-      </c>
-      <c r="S56" t="n">
-        <v>10</v>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT56" t="inlineStr"/>
-      <c r="AW56" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>112605497</v>
-      </c>
-      <c r="B57" t="n">
-        <v>88855</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>1962</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Vaddporing</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Anomoporia kamtschatica</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>Åmsele, Vb</t>
-        </is>
-      </c>
-      <c r="Q57" t="n">
-        <v>713221</v>
-      </c>
-      <c r="R57" t="n">
-        <v>7163456</v>
-      </c>
-      <c r="S57" t="n">
-        <v>10</v>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT57" t="inlineStr"/>
-      <c r="AW57" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>112605491</v>
-      </c>
-      <c r="B58" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>Åmsele, Vb</t>
-        </is>
-      </c>
-      <c r="Q58" t="n">
-        <v>713321</v>
-      </c>
-      <c r="R58" t="n">
-        <v>7163479</v>
-      </c>
-      <c r="S58" t="n">
-        <v>10</v>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT58" t="inlineStr"/>
-      <c r="AW58" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>112605509</v>
-      </c>
-      <c r="B59" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>Åmsele, Vb</t>
-        </is>
-      </c>
-      <c r="Q59" t="n">
-        <v>713235</v>
-      </c>
-      <c r="R59" t="n">
-        <v>7163391</v>
-      </c>
-      <c r="S59" t="n">
-        <v>10</v>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT59" t="inlineStr"/>
-      <c r="AW59" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>112605502</v>
-      </c>
-      <c r="B60" t="n">
-        <v>5473</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
-        <v>101410</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Reliktbock</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Nothorhina muricata</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>Åmsele, Vb</t>
-        </is>
-      </c>
-      <c r="Q60" t="n">
-        <v>713159</v>
-      </c>
-      <c r="R60" t="n">
-        <v>7163545</v>
-      </c>
-      <c r="S60" t="n">
-        <v>10</v>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT60" t="inlineStr"/>
-      <c r="AW60" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>112610147</v>
-      </c>
-      <c r="B61" t="n">
-        <v>91055</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>5966</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Motaggsvamp</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>Holmträsk, Vb</t>
-        </is>
-      </c>
-      <c r="Q61" t="n">
-        <v>713310</v>
-      </c>
-      <c r="R61" t="n">
-        <v>7163504</v>
-      </c>
-      <c r="S61" t="n">
-        <v>10</v>
-      </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AA61" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT61" t="inlineStr"/>
-      <c r="AW61" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>112610151</v>
-      </c>
-      <c r="B62" t="n">
-        <v>78448</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>Holmträsk, Vb</t>
-        </is>
-      </c>
-      <c r="Q62" t="n">
-        <v>713221</v>
-      </c>
-      <c r="R62" t="n">
-        <v>7163494</v>
-      </c>
-      <c r="S62" t="n">
-        <v>10</v>
-      </c>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y62" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AA62" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT62" t="inlineStr"/>
-      <c r="AW62" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>112610146</v>
-      </c>
-      <c r="B63" t="n">
-        <v>77608</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>6446</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Carbonicola anthracophila</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>Holmträsk, Vb</t>
-        </is>
-      </c>
-      <c r="Q63" t="n">
-        <v>713272</v>
-      </c>
-      <c r="R63" t="n">
-        <v>7163536</v>
-      </c>
-      <c r="S63" t="n">
-        <v>10</v>
-      </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT63" t="inlineStr"/>
-      <c r="AW63" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>112605499</v>
-      </c>
-      <c r="B64" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>Åmsele, Vb</t>
-        </is>
-      </c>
-      <c r="Q64" t="n">
-        <v>713176</v>
-      </c>
-      <c r="R64" t="n">
-        <v>7163502</v>
-      </c>
-      <c r="S64" t="n">
-        <v>10</v>
-      </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT64" t="inlineStr"/>
-      <c r="AW64" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>112605490</v>
-      </c>
-      <c r="B65" t="n">
-        <v>91055</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>5966</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Motaggsvamp</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>Åmsele, Vb</t>
-        </is>
-      </c>
-      <c r="Q65" t="n">
-        <v>713311</v>
-      </c>
-      <c r="R65" t="n">
-        <v>7163502</v>
-      </c>
-      <c r="S65" t="n">
-        <v>10</v>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT65" t="inlineStr"/>
-      <c r="AW65" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>112605507</v>
-      </c>
-      <c r="B66" t="n">
-        <v>78448</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E66" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>Åmsele, Vb</t>
-        </is>
-      </c>
-      <c r="Q66" t="n">
-        <v>713189</v>
-      </c>
-      <c r="R66" t="n">
-        <v>7163445</v>
-      </c>
-      <c r="S66" t="n">
-        <v>10</v>
-      </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y66" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT66" t="inlineStr"/>
-      <c r="AW66" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>112605500</v>
-      </c>
-      <c r="B67" t="n">
-        <v>77527</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
-        <v>353</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Dvärgbägarlav</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Cladonia parasitica</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>Åmsele, Vb</t>
-        </is>
-      </c>
-      <c r="Q67" t="n">
-        <v>713200</v>
-      </c>
-      <c r="R67" t="n">
-        <v>7163524</v>
-      </c>
-      <c r="S67" t="n">
-        <v>10</v>
-      </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT67" t="inlineStr"/>
-      <c r="AW67" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>112605486</v>
-      </c>
-      <c r="B68" t="n">
-        <v>5473</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
-        <v>101410</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Reliktbock</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Nothorhina muricata</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>Åmsele, Vb</t>
-        </is>
-      </c>
-      <c r="Q68" t="n">
-        <v>713156</v>
-      </c>
-      <c r="R68" t="n">
-        <v>7163518</v>
-      </c>
-      <c r="S68" t="n">
-        <v>10</v>
-      </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W68" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AA68" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT68" t="inlineStr"/>
-      <c r="AW68" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>112610156</v>
-      </c>
-      <c r="B69" t="n">
-        <v>77609</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>Holmträsk, Vb</t>
-        </is>
-      </c>
-      <c r="Q69" t="n">
-        <v>713141</v>
-      </c>
-      <c r="R69" t="n">
-        <v>7163575</v>
-      </c>
-      <c r="S69" t="n">
-        <v>10</v>
-      </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT69" t="inlineStr"/>
-      <c r="AW69" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>112610148</v>
-      </c>
-      <c r="B70" t="n">
-        <v>78448</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>Holmträsk, Vb</t>
-        </is>
-      </c>
-      <c r="Q70" t="n">
-        <v>713426</v>
-      </c>
-      <c r="R70" t="n">
-        <v>7163462</v>
-      </c>
-      <c r="S70" t="n">
-        <v>10</v>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT70" t="inlineStr"/>
-      <c r="AW70" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>112605495</v>
-      </c>
-      <c r="B71" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>Åmsele, Vb</t>
-        </is>
-      </c>
-      <c r="Q71" t="n">
-        <v>713338</v>
-      </c>
-      <c r="R71" t="n">
-        <v>7163452</v>
-      </c>
-      <c r="S71" t="n">
-        <v>10</v>
-      </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT71" t="inlineStr"/>
-      <c r="AW71" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>112605484</v>
-      </c>
-      <c r="B72" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>Åmsele, Vb</t>
-        </is>
-      </c>
-      <c r="Q72" t="n">
-        <v>713354</v>
-      </c>
-      <c r="R72" t="n">
-        <v>7163485</v>
-      </c>
-      <c r="S72" t="n">
-        <v>10</v>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AA72" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT72" t="inlineStr"/>
-      <c r="AW72" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>112605496</v>
-      </c>
-      <c r="B73" t="n">
-        <v>56768</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>Åmsele, Vb</t>
-        </is>
-      </c>
-      <c r="Q73" t="n">
-        <v>713260</v>
-      </c>
-      <c r="R73" t="n">
-        <v>7163415</v>
-      </c>
-      <c r="S73" t="n">
-        <v>10</v>
-      </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W73" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AA73" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT73" t="inlineStr"/>
-      <c r="AW73" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>112605489</v>
-      </c>
-      <c r="B74" t="n">
-        <v>77608</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
-        <v>6446</v>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Carbonicola anthracophila</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>Åmsele, Vb</t>
-        </is>
-      </c>
-      <c r="Q74" t="n">
-        <v>713278</v>
-      </c>
-      <c r="R74" t="n">
-        <v>7163530</v>
-      </c>
-      <c r="S74" t="n">
-        <v>10</v>
-      </c>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W74" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y74" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AA74" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT74" t="inlineStr"/>
-      <c r="AW74" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>112610153</v>
-      </c>
-      <c r="B75" t="n">
-        <v>77527</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E75" t="n">
-        <v>353</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Dvärgbägarlav</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Cladonia parasitica</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>Holmträsk, Vb</t>
-        </is>
-      </c>
-      <c r="Q75" t="n">
-        <v>713202</v>
-      </c>
-      <c r="R75" t="n">
-        <v>7163525</v>
-      </c>
-      <c r="S75" t="n">
-        <v>10</v>
-      </c>
-      <c r="T75" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V75" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W75" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y75" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AA75" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT75" t="inlineStr"/>
-      <c r="AW75" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>112610150</v>
-      </c>
-      <c r="B76" t="n">
-        <v>88855</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E76" t="n">
-        <v>1962</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Vaddporing</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Anomoporia kamtschatica</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>Holmträsk, Vb</t>
-        </is>
-      </c>
-      <c r="Q76" t="n">
-        <v>713222</v>
-      </c>
-      <c r="R76" t="n">
-        <v>7163450</v>
-      </c>
-      <c r="S76" t="n">
-        <v>10</v>
-      </c>
-      <c r="T76" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W76" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT76" t="inlineStr"/>
-      <c r="AW76" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 65389-2021 artfynd.xlsx
+++ b/artfynd/A 65389-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY49"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109910824</v>
+        <v>112605494</v>
       </c>
       <c r="B2" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>713155.4712538944</v>
+        <v>713426</v>
       </c>
       <c r="R2" t="n">
-        <v>7163538.981388154</v>
+        <v>7163462</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109909759</v>
+        <v>112605500</v>
       </c>
       <c r="B3" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,34 +788,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Holmträsk, Vb</t>
+          <t>Åmsele, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>713140.8316085221</v>
+        <v>713200</v>
       </c>
       <c r="R3" t="n">
-        <v>7163575.089193221</v>
+        <v>7163524</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,19 +845,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -909,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>109910807</v>
+        <v>112610149</v>
       </c>
       <c r="B4" t="n">
-        <v>5426</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,34 +890,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101410</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Åmsele, Vb</t>
+          <t>Holmträsk, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>713155.6280803431</v>
+        <v>713425</v>
       </c>
       <c r="R4" t="n">
-        <v>7163518.265564563</v>
+        <v>7163461</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,19 +947,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1026,15 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>109910821</v>
+        <v>112610153</v>
       </c>
       <c r="B5" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1062,14 +1012,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Åmsele, Vb</t>
+          <t>Holmträsk, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>713199.7607304036</v>
+        <v>713202</v>
       </c>
       <c r="R5" t="n">
-        <v>7163523.954035972</v>
+        <v>7163525</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,19 +1049,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1143,15 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>109909755</v>
+        <v>112605497</v>
       </c>
       <c r="B6" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1159,34 +1094,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>1962</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Holmträsk, Vb</t>
+          <t>Åmsele, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>713174.1039364932</v>
+        <v>713221</v>
       </c>
       <c r="R6" t="n">
-        <v>7163501.426179605</v>
+        <v>7163456</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,19 +1151,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1260,50 +1185,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>109910814</v>
+        <v>112610150</v>
       </c>
       <c r="B7" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Åmsele, Vb</t>
+          <t>Holmträsk, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>713448.3429063931</v>
+        <v>713222</v>
       </c>
       <c r="R7" t="n">
-        <v>7163468.86817537</v>
+        <v>7163450</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,19 +1253,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1377,37 +1287,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>109910809</v>
+        <v>112605410</v>
       </c>
       <c r="B8" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1417,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>713227.9087171451</v>
+        <v>713334</v>
       </c>
       <c r="R8" t="n">
-        <v>7163430.930171588</v>
+        <v>7163483</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1447,22 +1352,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-03</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1494,19 +1389,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>109909749</v>
+        <v>112605484</v>
       </c>
       <c r="B9" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1530,14 +1420,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Holmträsk, Vb</t>
+          <t>Åmsele, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>713272.4469905663</v>
+        <v>713354</v>
       </c>
       <c r="R9" t="n">
-        <v>7163535.534355256</v>
+        <v>7163485</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1567,19 +1457,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1611,15 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>109909757</v>
+        <v>112605485</v>
       </c>
       <c r="B10" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1627,34 +1502,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Holmträsk, Vb</t>
+          <t>Åmsele, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>713158.6416541047</v>
+        <v>713274</v>
       </c>
       <c r="R10" t="n">
-        <v>7163543.090159578</v>
+        <v>7163512</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1684,19 +1559,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1728,15 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>109909752</v>
+        <v>112605487</v>
       </c>
       <c r="B11" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1744,34 +1604,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Holmträsk, Vb</t>
+          <t>Åmsele, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>713425.5026207233</v>
+        <v>713209</v>
       </c>
       <c r="R11" t="n">
-        <v>7163461.649423476</v>
+        <v>7163472</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1801,19 +1661,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1845,15 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>109909758</v>
+        <v>112605488</v>
       </c>
       <c r="B12" t="n">
-        <v>5426</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,34 +1706,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>101410</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Holmträsk, Vb</t>
+          <t>Åmsele, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>713142.2127369607</v>
+        <v>713228</v>
       </c>
       <c r="R12" t="n">
-        <v>7163573.890711676</v>
+        <v>7163431</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1918,19 +1763,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1962,15 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>109910826</v>
+        <v>112605491</v>
       </c>
       <c r="B13" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1978,21 +1808,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2002,10 +1832,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>713191.5971422412</v>
+        <v>713321</v>
       </c>
       <c r="R13" t="n">
-        <v>7163461.63147788</v>
+        <v>7163479</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2035,19 +1865,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2079,15 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>109910730</v>
+        <v>112605493</v>
       </c>
       <c r="B14" t="n">
-        <v>90639</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2095,21 +1910,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3100</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2119,10 +1934,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>713334.1115571423</v>
+        <v>713448</v>
       </c>
       <c r="R14" t="n">
-        <v>7163482.433639663</v>
+        <v>7163469</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2149,22 +1964,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-11-03</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-11-03</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-31</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2196,15 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>109909750</v>
+        <v>112605495</v>
       </c>
       <c r="B15" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2212,34 +2012,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Holmträsk, Vb</t>
+          <t>Åmsele, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>713310.1096984316</v>
+        <v>713338</v>
       </c>
       <c r="R15" t="n">
-        <v>7163504.066011604</v>
+        <v>7163452</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2269,19 +2069,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2313,19 +2103,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>109910831</v>
+        <v>112605499</v>
       </c>
       <c r="B16" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2353,10 +2138,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>713234.5864448837</v>
+        <v>713176</v>
       </c>
       <c r="R16" t="n">
-        <v>7163391.239048198</v>
+        <v>7163502</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2386,19 +2171,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2430,15 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>109910828</v>
+        <v>112605503</v>
       </c>
       <c r="B17" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2446,21 +2216,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2470,10 +2240,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>713188.8409577697</v>
+        <v>713155</v>
       </c>
       <c r="R17" t="n">
-        <v>7163445.460670043</v>
+        <v>7163539</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2503,19 +2273,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2547,15 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>109910817</v>
+        <v>112605506</v>
       </c>
       <c r="B18" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2563,21 +2318,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2587,10 +2342,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>713260.1834900994</v>
+        <v>713190</v>
       </c>
       <c r="R18" t="n">
-        <v>7163414.627599885</v>
+        <v>7163460</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2620,19 +2375,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2664,19 +2409,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>109910808</v>
+        <v>112605509</v>
       </c>
       <c r="B19" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2704,10 +2444,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>713209.4639143429</v>
+        <v>713234</v>
       </c>
       <c r="R19" t="n">
-        <v>7163471.953819063</v>
+        <v>7163391</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2737,19 +2477,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2781,15 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>109909753</v>
+        <v>112610145</v>
       </c>
       <c r="B20" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2797,21 +2522,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2821,10 +2546,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>713221.8185952969</v>
+        <v>713230</v>
       </c>
       <c r="R20" t="n">
-        <v>7163449.934662092</v>
+        <v>7163429</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2854,19 +2579,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2898,15 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>109909751</v>
+        <v>112610152</v>
       </c>
       <c r="B21" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2914,21 +2624,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2938,10 +2648,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>713425.5026207233</v>
+        <v>713174</v>
       </c>
       <c r="R21" t="n">
-        <v>7163461.649423476</v>
+        <v>7163501</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2971,19 +2681,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3015,15 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>109909754</v>
+        <v>112605490</v>
       </c>
       <c r="B22" t="n">
-        <v>88476</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3031,34 +2726,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1962</v>
+        <v>5966</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Holmträsk, Vb</t>
+          <t>Åmsele, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>713220.8928795417</v>
+        <v>713311</v>
       </c>
       <c r="R22" t="n">
-        <v>7163493.915147737</v>
+        <v>7163502</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3088,19 +2783,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3132,15 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>109910815</v>
+        <v>112610147</v>
       </c>
       <c r="B23" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3148,34 +2828,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>5966</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Åmsele, Vb</t>
+          <t>Holmträsk, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>713425.5026207233</v>
+        <v>713310</v>
       </c>
       <c r="R23" t="n">
-        <v>7163461.649423476</v>
+        <v>7163504</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3205,19 +2885,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3249,37 +2919,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>109910806</v>
+        <v>112605489</v>
       </c>
       <c r="B24" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3289,10 +2954,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>713273.6762816359</v>
+        <v>713278</v>
       </c>
       <c r="R24" t="n">
-        <v>7163511.871002888</v>
+        <v>7163530</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3322,19 +2987,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3366,37 +3021,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>109910820</v>
+        <v>112605505</v>
       </c>
       <c r="B25" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3406,10 +3056,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>713175.7645458361</v>
+        <v>713191</v>
       </c>
       <c r="R25" t="n">
-        <v>7163502.406359276</v>
+        <v>7163461</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3439,19 +3089,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3483,15 +3123,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>109910819</v>
+        <v>112610146</v>
       </c>
       <c r="B26" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3499,34 +3134,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Åmsele, Vb</t>
+          <t>Holmträsk, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>713209.3591374015</v>
+        <v>713273</v>
       </c>
       <c r="R26" t="n">
-        <v>7163485.764611806</v>
+        <v>7163536</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3556,19 +3191,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3600,15 +3225,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>109910830</v>
+        <v>112605492</v>
       </c>
       <c r="B27" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3640,10 +3260,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>713203.9961333454</v>
+        <v>713448</v>
       </c>
       <c r="R27" t="n">
-        <v>7163426.660596962</v>
+        <v>7163473</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3673,19 +3293,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3717,37 +3327,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>109910827</v>
+        <v>112605498</v>
       </c>
       <c r="B28" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3757,10 +3362,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>713189.5665984</v>
+        <v>713209</v>
       </c>
       <c r="R28" t="n">
-        <v>7163459.761674738</v>
+        <v>7163486</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3790,19 +3395,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -3834,15 +3429,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>109910810</v>
+        <v>112605507</v>
       </c>
       <c r="B29" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3850,21 +3440,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3874,10 +3464,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>713277.6019235936</v>
+        <v>713189</v>
       </c>
       <c r="R29" t="n">
-        <v>7163529.850985159</v>
+        <v>7163446</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3907,19 +3497,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -3951,15 +3531,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>109910825</v>
+        <v>112605508</v>
       </c>
       <c r="B30" t="n">
-        <v>5426</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3967,21 +3542,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>101410</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3991,10 +3566,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>713142.6629788965</v>
+        <v>713204</v>
       </c>
       <c r="R30" t="n">
-        <v>7163542.832384868</v>
+        <v>7163427</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4024,19 +3599,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4068,37 +3633,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>109909756</v>
+        <v>112610148</v>
       </c>
       <c r="B31" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4108,10 +3668,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>713201.8515485525</v>
+        <v>713425</v>
       </c>
       <c r="R31" t="n">
-        <v>7163524.964424724</v>
+        <v>7163461</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4141,19 +3701,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4185,15 +3735,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>109910818</v>
+        <v>112610151</v>
       </c>
       <c r="B32" t="n">
-        <v>88476</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4201,34 +3746,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1962</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Åmsele, Vb</t>
+          <t>Holmträsk, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>713220.5357991222</v>
+        <v>713221</v>
       </c>
       <c r="R32" t="n">
-        <v>7163455.890102807</v>
+        <v>7163494</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4258,19 +3803,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4302,50 +3837,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>109910816</v>
+        <v>112610155</v>
       </c>
       <c r="B33" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Åmsele, Vb</t>
+          <t>Holmträsk, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>713337.5149978739</v>
+        <v>713142</v>
       </c>
       <c r="R33" t="n">
-        <v>7163452.445188347</v>
+        <v>7163574</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4375,19 +3905,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4419,15 +3939,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>109910823</v>
+        <v>112605486</v>
       </c>
       <c r="B34" t="n">
-        <v>5426</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5495</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4459,10 +3974,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>713159.3513208975</v>
+        <v>713156</v>
       </c>
       <c r="R34" t="n">
-        <v>7163545.299000438</v>
+        <v>7163518</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4492,19 +4007,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -4536,37 +4041,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>109910812</v>
+        <v>112605502</v>
       </c>
       <c r="B35" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5495</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>101410</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4576,10 +4076,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>713321.3554037845</v>
+        <v>713159</v>
       </c>
       <c r="R35" t="n">
-        <v>7163479.37859088</v>
+        <v>7163545</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4609,19 +4109,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -4653,37 +4143,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>109910804</v>
+        <v>112605504</v>
       </c>
       <c r="B36" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5495</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>101410</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4693,10 +4178,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>713354.2722309845</v>
+        <v>713142</v>
       </c>
       <c r="R36" t="n">
-        <v>7163484.713410687</v>
+        <v>7163543</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4726,19 +4211,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -4770,15 +4245,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>109909748</v>
+        <v>112610154</v>
       </c>
       <c r="B37" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5495</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4786,21 +4256,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>101410</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4810,10 +4280,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>713229.7503524562</v>
+        <v>713158</v>
       </c>
       <c r="R37" t="n">
-        <v>7163429.332162086</v>
+        <v>7163543</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4843,19 +4313,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -4887,15 +4347,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>109910822</v>
+        <v>112605496</v>
       </c>
       <c r="B38" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4903,21 +4358,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4927,10 +4382,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>713139.1710311332</v>
+        <v>713260</v>
       </c>
       <c r="R38" t="n">
-        <v>7163574.109053378</v>
+        <v>7163414</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4960,19 +4415,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -5004,15 +4449,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>109910811</v>
+        <v>112605501</v>
       </c>
       <c r="B39" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5020,21 +4460,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5966</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5044,10 +4484,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>713311.1210543601</v>
+        <v>713139</v>
       </c>
       <c r="R39" t="n">
-        <v>7163501.977961116</v>
+        <v>7163574</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5077,19 +4517,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -5121,15 +4551,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>112610154</v>
+        <v>112610156</v>
       </c>
       <c r="B40" t="n">
-        <v>5473</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5137,21 +4562,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>101410</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5161,10 +4586,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>713159</v>
+        <v>713141</v>
       </c>
       <c r="R40" t="n">
-        <v>7163543</v>
+        <v>7163575</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5225,969 +4650,6 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>112610152</v>
-      </c>
-      <c r="B41" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Holmträsk, Vb</t>
-        </is>
-      </c>
-      <c r="Q41" t="n">
-        <v>713174</v>
-      </c>
-      <c r="R41" t="n">
-        <v>7163501</v>
-      </c>
-      <c r="S41" t="n">
-        <v>10</v>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT41" t="inlineStr"/>
-      <c r="AW41" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>112610155</v>
-      </c>
-      <c r="B42" t="n">
-        <v>78448</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Holmträsk, Vb</t>
-        </is>
-      </c>
-      <c r="Q42" t="n">
-        <v>713142</v>
-      </c>
-      <c r="R42" t="n">
-        <v>7163574</v>
-      </c>
-      <c r="S42" t="n">
-        <v>10</v>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT42" t="inlineStr"/>
-      <c r="AW42" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>112610145</v>
-      </c>
-      <c r="B43" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>Holmträsk, Vb</t>
-        </is>
-      </c>
-      <c r="Q43" t="n">
-        <v>713230</v>
-      </c>
-      <c r="R43" t="n">
-        <v>7163429</v>
-      </c>
-      <c r="S43" t="n">
-        <v>10</v>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT43" t="inlineStr"/>
-      <c r="AW43" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>112610147</v>
-      </c>
-      <c r="B44" t="n">
-        <v>91055</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>5966</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Motaggsvamp</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>Holmträsk, Vb</t>
-        </is>
-      </c>
-      <c r="Q44" t="n">
-        <v>713310</v>
-      </c>
-      <c r="R44" t="n">
-        <v>7163504</v>
-      </c>
-      <c r="S44" t="n">
-        <v>10</v>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT44" t="inlineStr"/>
-      <c r="AW44" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>112610151</v>
-      </c>
-      <c r="B45" t="n">
-        <v>78448</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>Holmträsk, Vb</t>
-        </is>
-      </c>
-      <c r="Q45" t="n">
-        <v>713221</v>
-      </c>
-      <c r="R45" t="n">
-        <v>7163494</v>
-      </c>
-      <c r="S45" t="n">
-        <v>10</v>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT45" t="inlineStr"/>
-      <c r="AW45" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>112610146</v>
-      </c>
-      <c r="B46" t="n">
-        <v>77608</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>6446</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Carbonicola anthracophila</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>Holmträsk, Vb</t>
-        </is>
-      </c>
-      <c r="Q46" t="n">
-        <v>713272</v>
-      </c>
-      <c r="R46" t="n">
-        <v>7163536</v>
-      </c>
-      <c r="S46" t="n">
-        <v>10</v>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT46" t="inlineStr"/>
-      <c r="AW46" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>112610156</v>
-      </c>
-      <c r="B47" t="n">
-        <v>77609</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>Holmträsk, Vb</t>
-        </is>
-      </c>
-      <c r="Q47" t="n">
-        <v>713141</v>
-      </c>
-      <c r="R47" t="n">
-        <v>7163575</v>
-      </c>
-      <c r="S47" t="n">
-        <v>10</v>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT47" t="inlineStr"/>
-      <c r="AW47" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>112610153</v>
-      </c>
-      <c r="B48" t="n">
-        <v>77527</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>353</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Dvärgbägarlav</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Cladonia parasitica</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>Holmträsk, Vb</t>
-        </is>
-      </c>
-      <c r="Q48" t="n">
-        <v>713202</v>
-      </c>
-      <c r="R48" t="n">
-        <v>7163525</v>
-      </c>
-      <c r="S48" t="n">
-        <v>10</v>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT48" t="inlineStr"/>
-      <c r="AW48" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>112610150</v>
-      </c>
-      <c r="B49" t="n">
-        <v>88855</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>1962</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Vaddporing</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Anomoporia kamtschatica</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>Holmträsk, Vb</t>
-        </is>
-      </c>
-      <c r="Q49" t="n">
-        <v>713222</v>
-      </c>
-      <c r="R49" t="n">
-        <v>7163450</v>
-      </c>
-      <c r="S49" t="n">
-        <v>10</v>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT49" t="inlineStr"/>
-      <c r="AW49" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 65389-2021 artfynd.xlsx
+++ b/artfynd/A 65389-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AZ40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112605494</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112605500</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610149</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610153</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112605497</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610150</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112605410</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,6 +1528,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112605484</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1590,6 +1635,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112605485</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1692,6 +1742,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112605487</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1794,6 +1849,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112605488</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1896,6 +1956,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112605491</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1998,6 +2063,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112605493</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2100,6 +2170,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112605495</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2202,6 +2277,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112605499</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2304,6 +2384,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112605503</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2406,6 +2491,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112605506</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2508,6 +2598,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112605509</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2610,6 +2705,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610145</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2712,6 +2812,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610152</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2814,6 +2919,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112605490</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2916,6 +3026,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610147</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3018,6 +3133,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112605489</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3120,6 +3240,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112605505</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3222,6 +3347,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610146</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3324,6 +3454,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112605492</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3426,6 +3561,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112605498</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3528,6 +3668,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112605507</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3630,6 +3775,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112605508</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3732,6 +3882,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610148</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3834,6 +3989,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610151</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3936,6 +4096,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610155</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4038,6 +4203,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112605486</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4140,6 +4310,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112605502</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4242,6 +4417,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112605504</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4344,6 +4524,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610154</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4446,6 +4631,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112605496</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4548,6 +4738,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112605501</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4650,8 +4845,54 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610156</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>